--- a/data/trans_orig/MCS12_SP_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2007</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>98287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130222</t>
+          <t>128564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120850</t>
+          <t>118650</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153438</t>
+          <t>153441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227049</t>
+          <t>225734</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>272842</t>
+          <t>273363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142788</t>
+          <t>144446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175977</t>
+          <t>174723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107400</t>
+          <t>107397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>142188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261006</t>
+          <t>260485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>306799</t>
+          <t>308114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>253213</t>
+          <t>251902</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298697</t>
+          <t>296146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>321851</t>
+          <t>320626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363890</t>
+          <t>364253</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>587179</t>
+          <t>585875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>648459</t>
+          <t>648448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194378</t>
+          <t>196929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>239862</t>
+          <t>241173</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140059</t>
+          <t>139696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182098</t>
+          <t>183323</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348565</t>
+          <t>348576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409845</t>
+          <t>411149</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71028</t>
+          <t>69188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102836</t>
+          <t>103449</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119670</t>
+          <t>118394</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157517</t>
+          <t>155407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202168</t>
+          <t>199572</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247787</t>
+          <t>248076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>216010</t>
+          <t>215397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247818</t>
+          <t>249658</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177895</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>215742</t>
+          <t>217018</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406471</t>
+          <t>406182</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>452090</t>
+          <t>454686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>130378</t>
+          <t>129829</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168549</t>
+          <t>167361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167325</t>
+          <t>168786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205884</t>
+          <t>205756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>312157</t>
+          <t>309828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364356</t>
+          <t>362832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190122</t>
+          <t>191310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228293</t>
+          <t>228842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165572</t>
+          <t>165700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>204131</t>
+          <t>202670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>365771</t>
+          <t>367295</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417970</t>
+          <t>420299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,57%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83772</t>
+          <t>82367</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111496</t>
+          <t>111106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109985</t>
+          <t>110669</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137513</t>
+          <t>139053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200728</t>
+          <t>202639</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242212</t>
+          <t>242280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91812</t>
+          <t>92202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119536</t>
+          <t>120941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70155</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97683</t>
+          <t>96999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168764</t>
+          <t>168696</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>210248</t>
+          <t>208337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77160</t>
+          <t>78172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107618</t>
+          <t>109732</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112775</t>
+          <t>112979</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>148014</t>
+          <t>145455</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>199491</t>
+          <t>200634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>242750</t>
+          <t>246048</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163193</t>
+          <t>161079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193651</t>
+          <t>192639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>130130</t>
+          <t>132689</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165369</t>
+          <t>165165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>306205</t>
+          <t>302907</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>349464</t>
+          <t>348321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191279</t>
+          <t>193679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239433</t>
+          <t>239938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287657</t>
+          <t>287707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>338077</t>
+          <t>336946</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493250</t>
+          <t>493496</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>562246</t>
+          <t>560623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>375594</t>
+          <t>375089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>423748</t>
+          <t>421348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>300142</t>
+          <t>301273</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>350562</t>
+          <t>350512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>691000</t>
+          <t>692623</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>759996</t>
+          <t>759750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>360191</t>
+          <t>362728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>412225</t>
+          <t>417942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>430139</t>
+          <t>429087</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>487109</t>
+          <t>485345</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>805900</t>
+          <t>804644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>886728</t>
+          <t>883420</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331570</t>
+          <t>325853</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>383604</t>
+          <t>381067</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>296402</t>
+          <t>298166</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>353372</t>
+          <t>354424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>640578</t>
+          <t>643886</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>721406</t>
+          <t>722662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1356877</t>
+          <t>1359326</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1473889</t>
+          <t>1474346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1773088</t>
+          <t>1770768</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1890301</t>
+          <t>1893868</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3167492</t>
+          <t>3159395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3328852</t>
+          <t>3321312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1802654</t>
+          <t>1802197</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1919666</t>
+          <t>1917217</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1488896</t>
+          <t>1485329</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1606109</t>
+          <t>1608429</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3326889</t>
+          <t>3334429</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3488249</t>
+          <t>3496346</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2012</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148710</t>
+          <t>146499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180885</t>
+          <t>182932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198189</t>
+          <t>198065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229042</t>
+          <t>229456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>356042</t>
+          <t>354103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>402925</t>
+          <t>402159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>113853</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146028</t>
+          <t>148239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89056</t>
+          <t>89180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179058</t>
+          <t>179824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225941</t>
+          <t>227880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109620</t>
+          <t>108206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149953</t>
+          <t>150558</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195147</t>
+          <t>195345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242767</t>
+          <t>240743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>310984</t>
+          <t>315881</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>376262</t>
+          <t>379294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355574</t>
+          <t>354969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>395907</t>
+          <t>397321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280998</t>
+          <t>283022</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328618</t>
+          <t>328420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>653030</t>
+          <t>649998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718308</t>
+          <t>713411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,31%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141181</t>
+          <t>140067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178139</t>
+          <t>177119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207288</t>
+          <t>207125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244412</t>
+          <t>244189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>358570</t>
+          <t>357979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>410738</t>
+          <t>409743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>146927</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>182865</t>
+          <t>183979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96608</t>
+          <t>96831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133732</t>
+          <t>133895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>255323</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306496</t>
+          <t>307087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220124</t>
+          <t>220272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>258877</t>
+          <t>259383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>273504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>308735</t>
+          <t>307641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505850</t>
+          <t>506012</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>557657</t>
+          <t>555130</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115105</t>
+          <t>114599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153858</t>
+          <t>153710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80216</t>
+          <t>81310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116303</t>
+          <t>115447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205276</t>
+          <t>207803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>257083</t>
+          <t>256921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62711</t>
+          <t>63217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>91340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96254</t>
+          <t>96054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125863</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167175</t>
+          <t>165646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>211635</t>
+          <t>209189</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120328</t>
+          <t>121278</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149907</t>
+          <t>149401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93728</t>
+          <t>93071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123337</t>
+          <t>123537</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220574</t>
+          <t>223020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265034</t>
+          <t>266563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,67%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>132128</t>
+          <t>130088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>166504</t>
+          <t>165772</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161274</t>
+          <t>161569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>194071</t>
+          <t>195322</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>300246</t>
+          <t>300652</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>346569</t>
+          <t>349178</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,03%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107477</t>
+          <t>108209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>141853</t>
+          <t>143893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85960</t>
+          <t>84709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118757</t>
+          <t>118462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>207443</t>
+          <t>204834</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253766</t>
+          <t>253360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>338201</t>
+          <t>338897</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>391440</t>
+          <t>394137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>425048</t>
+          <t>427250</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>477333</t>
+          <t>479121</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>786325</t>
+          <t>779124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>860465</t>
+          <t>857495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>271348</t>
+          <t>268651</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>324587</t>
+          <t>323891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>216520</t>
+          <t>214732</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>268805</t>
+          <t>266603</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>496176</t>
+          <t>499146</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>570316</t>
+          <t>577517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>368126</t>
+          <t>363522</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>424735</t>
+          <t>422891</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>480493</t>
+          <t>482148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>538355</t>
+          <t>537852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>864740</t>
+          <t>859911</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>946381</t>
+          <t>945633</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,99%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>354363</t>
+          <t>356207</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>410972</t>
+          <t>415576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>285498</t>
+          <t>286001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>343360</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>656570</t>
+          <t>657318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>738211</t>
+          <t>743040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1620190</t>
+          <t>1621155</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1738378</t>
+          <t>1735304</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2141823</t>
+          <t>2141157</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2259257</t>
+          <t>2255406</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3790831</t>
+          <t>3799360</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3959656</t>
+          <t>3968661</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1688401</t>
+          <t>1691475</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1806589</t>
+          <t>1805624</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1299052</t>
+          <t>1302903</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1416486</t>
+          <t>1417152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3025432</t>
+          <t>3016427</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3194257</t>
+          <t>3185728</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2016</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146787</t>
+          <t>147435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182744</t>
+          <t>182943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178758</t>
+          <t>179010</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210427</t>
+          <t>211294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>337028</t>
+          <t>336543</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385593</t>
+          <t>381315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111017</t>
+          <t>110818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146974</t>
+          <t>146326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78276</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109945</t>
+          <t>109693</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196871</t>
+          <t>201149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245436</t>
+          <t>245921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89082</t>
+          <t>89998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127440</t>
+          <t>126215</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>129533</t>
+          <t>131606</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173698</t>
+          <t>174526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>231534</t>
+          <t>229320</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287688</t>
+          <t>285717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>375135</t>
+          <t>376360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>413493</t>
+          <t>412577</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>349386</t>
+          <t>348558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>393551</t>
+          <t>391478</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>737971</t>
+          <t>739942</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>794125</t>
+          <t>796339</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139338</t>
+          <t>139000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>174585</t>
+          <t>173422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187390</t>
+          <t>187338</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>225569</t>
+          <t>222503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336351</t>
+          <t>336164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385057</t>
+          <t>385729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143980</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179227</t>
+          <t>179565</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110740</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148919</t>
+          <t>148971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269817</t>
+          <t>269145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318523</t>
+          <t>318710</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,67%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145536</t>
+          <t>143414</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>184297</t>
+          <t>182822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189955</t>
+          <t>189842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230051</t>
+          <t>231103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344226</t>
+          <t>344531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399798</t>
+          <t>402183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185667</t>
+          <t>187142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224428</t>
+          <t>226550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>157232</t>
+          <t>156180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197328</t>
+          <t>197441</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>357449</t>
+          <t>355064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>413021</t>
+          <t>412716</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,5%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>172619</t>
+          <t>173351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191698</t>
+          <t>191828</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181433</t>
+          <t>181304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200952</t>
+          <t>200115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>361252</t>
+          <t>359584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386744</t>
+          <t>386022</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>18472</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37154</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43064</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68556</t>
+          <t>70224</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78103</t>
+          <t>76410</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109735</t>
+          <t>107505</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107565</t>
+          <t>108670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139740</t>
+          <t>141912</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193258</t>
+          <t>194637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239510</t>
+          <t>239882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153388</t>
+          <t>155618</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185020</t>
+          <t>186713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133375</t>
+          <t>131203</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165550</t>
+          <t>164445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296728</t>
+          <t>296356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342980</t>
+          <t>341601</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>319200</t>
+          <t>322642</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>372401</t>
+          <t>376137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369664</t>
+          <t>369187</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>424183</t>
+          <t>422823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>709595</t>
+          <t>707831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>784534</t>
+          <t>782686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>284157</t>
+          <t>280421</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>337358</t>
+          <t>333916</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>267111</t>
+          <t>268471</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321630</t>
+          <t>322107</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>563318</t>
+          <t>565166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>638257</t>
+          <t>640021</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>395286</t>
+          <t>390290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>450899</t>
+          <t>447412</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>438268</t>
+          <t>439059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>497576</t>
+          <t>499797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>846023</t>
+          <t>846689</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>927260</t>
+          <t>931619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>327684</t>
+          <t>331171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>383297</t>
+          <t>388293</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>328591</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387899</t>
+          <t>387108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>677490</t>
+          <t>673131</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>758727</t>
+          <t>758061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1575082</t>
+          <t>1578751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1691855</t>
+          <t>1701411</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1882208</t>
+          <t>1884984</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2005086</t>
+          <t>2012236</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3498469</t>
+          <t>3483912</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3664912</t>
+          <t>3659063</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1702495</t>
+          <t>1692939</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1819268</t>
+          <t>1815599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1539456</t>
+          <t>1532306</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1662334</t>
+          <t>1659558</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3273980</t>
+          <t>3279829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3440423</t>
+          <t>3454980</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana (53.5790) de la puntuación del componente de salud mental (SF12) en 2023</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) en 2023 (tasa de respuesta: 99,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85858</t>
+          <t>85062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127112</t>
+          <t>124230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90431</t>
+          <t>89080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118560</t>
+          <t>117901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185404</t>
+          <t>185162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236448</t>
+          <t>234319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>184331</t>
+          <t>187213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>225585</t>
+          <t>226381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171075</t>
+          <t>171734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199204</t>
+          <t>200555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>364629</t>
+          <t>366758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415673</t>
+          <t>415915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,19%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118648</t>
+          <t>117298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168251</t>
+          <t>171214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174952</t>
+          <t>174341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>213600</t>
+          <t>215320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305562</t>
+          <t>305548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372878</t>
+          <t>372395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349268</t>
+          <t>346305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398871</t>
+          <t>400221</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299977</t>
+          <t>298257</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>338625</t>
+          <t>339236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658218</t>
+          <t>658701</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725534</t>
+          <t>725548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100647</t>
+          <t>99957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>114426</t>
+          <t>113783</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145209</t>
+          <t>144472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192899</t>
+          <t>192313</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232245</t>
+          <t>234516</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213430</t>
+          <t>214120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244876</t>
+          <t>243465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198896</t>
+          <t>199633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229679</t>
+          <t>230322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>425937</t>
+          <t>423666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>465283</t>
+          <t>465869</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,78%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79694</t>
+          <t>80733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>120029</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169082</t>
+          <t>164430</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>312186</t>
+          <t>314072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262976</t>
+          <t>264951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448241</t>
+          <t>457321</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186184</t>
+          <t>186155</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226490</t>
+          <t>225451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158293</t>
+          <t>156407</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301397</t>
+          <t>306049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328422</t>
+          <t>319342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>513687</t>
+          <t>511712</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,89%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125461</t>
+          <t>125531</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144929</t>
+          <t>145966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>164323</t>
+          <t>163381</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179969</t>
+          <t>179497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294278</t>
+          <t>294601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320025</t>
+          <t>321481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33310</t>
+          <t>32273</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52778</t>
+          <t>52708</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>27150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42324</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64861</t>
+          <t>63405</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90608</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>78591</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107179</t>
+          <t>106841</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85971</t>
+          <t>84162</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108900</t>
+          <t>109593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170028</t>
+          <t>172123</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207434</t>
+          <t>209295</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161985</t>
+          <t>162323</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190548</t>
+          <t>190573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148156</t>
+          <t>147463</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>171085</t>
+          <t>172894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>318786</t>
+          <t>316925</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>356192</t>
+          <t>354097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293994</t>
+          <t>293769</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>357228</t>
+          <t>355192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>525494</t>
+          <t>525784</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>752701</t>
+          <t>734326</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>834341</t>
+          <t>837413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1140452</t>
+          <t>1156375</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>262673</t>
+          <t>264709</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>325907</t>
+          <t>326132</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>94163</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>321080</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>326313</t>
+          <t>310390</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>632424</t>
+          <t>629352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153188</t>
+          <t>153185</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>481867</t>
+          <t>480900</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>404927</t>
+          <t>407438</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>452266</t>
+          <t>452295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>480241</t>
+          <t>447793</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>925618</t>
+          <t>919980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>445317</t>
+          <t>446284</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773996</t>
+          <t>773999</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>262975</t>
+          <t>262946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310314</t>
+          <t>307803</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>716807</t>
+          <t>722445</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1162184</t>
+          <t>1194632</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>976902</t>
+          <t>1052445</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1447636</t>
+          <t>1456307</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1823309</t>
+          <t>1827309</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2243155</t>
+          <t>2268094</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2972898</t>
+          <t>2972143</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3602461</t>
+          <t>3633796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1996075</t>
+          <t>1987404</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2466809</t>
+          <t>2391266</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1400448</t>
+          <t>1375509</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1820294</t>
+          <t>1816294</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3484853</t>
+          <t>3453518</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4114416</t>
+          <t>4115171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98287</t>
+          <t>94973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128564</t>
+          <t>126542</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118650</t>
+          <t>120442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153441</t>
+          <t>153780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225734</t>
+          <t>221610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273363</t>
+          <t>270289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144446</t>
+          <t>146468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174723</t>
+          <t>178037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107397</t>
+          <t>107058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142188</t>
+          <t>140396</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260485</t>
+          <t>263559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>308114</t>
+          <t>312238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251902</t>
+          <t>253816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296146</t>
+          <t>299181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>320626</t>
+          <t>324544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>364253</t>
+          <t>365157</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>585875</t>
+          <t>585582</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>648448</t>
+          <t>647515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>196929</t>
+          <t>193894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241173</t>
+          <t>239259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>139696</t>
+          <t>138792</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>183323</t>
+          <t>179405</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348576</t>
+          <t>349509</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411149</t>
+          <t>411442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>70683</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103449</t>
+          <t>103792</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118394</t>
+          <t>119899</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155407</t>
+          <t>155769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199572</t>
+          <t>199451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>248076</t>
+          <t>248017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,91%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215397</t>
+          <t>215054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>249658</t>
+          <t>248163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180005</t>
+          <t>179643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>217018</t>
+          <t>215513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>406182</t>
+          <t>406241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454686</t>
+          <t>454807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129829</t>
+          <t>131177</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167361</t>
+          <t>167655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168786</t>
+          <t>169659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205756</t>
+          <t>206675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309828</t>
+          <t>312173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>362832</t>
+          <t>365007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>191310</t>
+          <t>191016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228842</t>
+          <t>227494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165700</t>
+          <t>164781</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>202670</t>
+          <t>201797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367295</t>
+          <t>365120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>420299</t>
+          <t>417954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82367</t>
+          <t>84343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111106</t>
+          <t>113225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110669</t>
+          <t>110984</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139053</t>
+          <t>138790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>202639</t>
+          <t>200252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242280</t>
+          <t>243244</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,19%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92202</t>
+          <t>90083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>120941</t>
+          <t>118965</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96999</t>
+          <t>96684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168696</t>
+          <t>167732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208337</t>
+          <t>210724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78172</t>
+          <t>78477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>109732</t>
+          <t>109252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112979</t>
+          <t>111149</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>145455</t>
+          <t>145762</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>200634</t>
+          <t>198990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>246048</t>
+          <t>243481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161079</t>
+          <t>161559</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192639</t>
+          <t>192334</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>132689</t>
+          <t>132382</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>165165</t>
+          <t>166995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302907</t>
+          <t>305474</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>348321</t>
+          <t>349965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>193679</t>
+          <t>190625</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>240050</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>287707</t>
+          <t>287100</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>336946</t>
+          <t>336976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>493496</t>
+          <t>494509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>560623</t>
+          <t>565978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>375089</t>
+          <t>374977</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>421348</t>
+          <t>424402</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301273</t>
+          <t>301243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>350512</t>
+          <t>351119</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>692623</t>
+          <t>687268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>759750</t>
+          <t>758737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,54%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>362728</t>
+          <t>359543</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>417942</t>
+          <t>413107</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>429087</t>
+          <t>429282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>485345</t>
+          <t>486040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>804644</t>
+          <t>803926</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>883420</t>
+          <t>885688</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>325853</t>
+          <t>330688</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>381067</t>
+          <t>384252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>298166</t>
+          <t>297471</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>354424</t>
+          <t>354229</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>643886</t>
+          <t>641618</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>722662</t>
+          <t>723380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1359326</t>
+          <t>1359732</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1474346</t>
+          <t>1472819</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1770768</t>
+          <t>1773654</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1893868</t>
+          <t>1890895</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3159395</t>
+          <t>3161364</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3321312</t>
+          <t>3326987</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,99%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1802197</t>
+          <t>1803724</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1917217</t>
+          <t>1916811</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1485329</t>
+          <t>1488302</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1608429</t>
+          <t>1605543</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3334429</t>
+          <t>3328754</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3496346</t>
+          <t>3494377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,5%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146499</t>
+          <t>148414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182932</t>
+          <t>183820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>198065</t>
+          <t>197152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229456</t>
+          <t>228574</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354103</t>
+          <t>355243</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>402159</t>
+          <t>403986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111806</t>
+          <t>110918</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148239</t>
+          <t>146324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57789</t>
+          <t>58671</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>89180</t>
+          <t>90093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179824</t>
+          <t>177997</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227880</t>
+          <t>226740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108206</t>
+          <t>108070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>150558</t>
+          <t>148295</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195345</t>
+          <t>192034</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240743</t>
+          <t>242116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>315881</t>
+          <t>315477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379294</t>
+          <t>378290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>354969</t>
+          <t>357232</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397321</t>
+          <t>397457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283022</t>
+          <t>281649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328420</t>
+          <t>331731</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649998</t>
+          <t>651002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713411</t>
+          <t>713815</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,35%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>139675</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177119</t>
+          <t>175411</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>207125</t>
+          <t>208132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244189</t>
+          <t>242365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357979</t>
+          <t>359014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409743</t>
+          <t>411399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,86%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>146927</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183979</t>
+          <t>184371</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96831</t>
+          <t>98655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133895</t>
+          <t>132888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255323</t>
+          <t>253667</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307087</t>
+          <t>306052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,02%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>220272</t>
+          <t>219844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259383</t>
+          <t>259354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>273504</t>
+          <t>271591</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307641</t>
+          <t>308114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>506012</t>
+          <t>500926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>555130</t>
+          <t>557254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114599</t>
+          <t>114628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153710</t>
+          <t>154138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81310</t>
+          <t>80837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115447</t>
+          <t>117360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207803</t>
+          <t>205679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256921</t>
+          <t>262007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63217</t>
+          <t>64306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91340</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>96054</t>
+          <t>96855</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>125129</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165646</t>
+          <t>169113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>209189</t>
+          <t>209822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121278</t>
+          <t>120181</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>149401</t>
+          <t>148312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93071</t>
+          <t>94462</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123537</t>
+          <t>122736</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223020</t>
+          <t>222387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>266563</t>
+          <t>263096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,87%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130088</t>
+          <t>132403</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>165772</t>
+          <t>163996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>161569</t>
+          <t>161167</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>195322</t>
+          <t>192141</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>300652</t>
+          <t>302181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>349178</t>
+          <t>350674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108209</t>
+          <t>109985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143893</t>
+          <t>141578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>87890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>118462</t>
+          <t>118864</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204834</t>
+          <t>203338</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>253360</t>
+          <t>251831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>338897</t>
+          <t>337530</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>394137</t>
+          <t>390727</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>427250</t>
+          <t>425212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>479121</t>
+          <t>479256</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>779124</t>
+          <t>779113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>857495</t>
+          <t>855383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268651</t>
+          <t>272061</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>323891</t>
+          <t>325258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>214732</t>
+          <t>214597</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>266603</t>
+          <t>268641</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>499146</t>
+          <t>501258</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577517</t>
+          <t>577528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>363522</t>
+          <t>362469</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>422891</t>
+          <t>421052</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>482148</t>
+          <t>482220</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>537852</t>
+          <t>539060</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>859911</t>
+          <t>863454</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>945633</t>
+          <t>945196</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>356207</t>
+          <t>358046</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>415576</t>
+          <t>416629</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>286001</t>
+          <t>284793</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>341705</t>
+          <t>341633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>657318</t>
+          <t>657755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>743040</t>
+          <t>739497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1621155</t>
+          <t>1617919</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1735304</t>
+          <t>1741217</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2141157</t>
+          <t>2141732</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2255406</t>
+          <t>2263726</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3799360</t>
+          <t>3797016</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3968661</t>
+          <t>3961862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1691475</t>
+          <t>1685562</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1805624</t>
+          <t>1808860</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1302903</t>
+          <t>1294583</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1417152</t>
+          <t>1416577</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3016427</t>
+          <t>3023226</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3185728</t>
+          <t>3188072</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,64%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>147435</t>
+          <t>145714</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>181620</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>179010</t>
+          <t>176503</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211294</t>
+          <t>209655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>336543</t>
+          <t>333677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>381315</t>
+          <t>386243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110818</t>
+          <t>112141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146326</t>
+          <t>148047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>79048</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109693</t>
+          <t>112200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>201149</t>
+          <t>196221</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245921</t>
+          <t>248787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,71%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89998</t>
+          <t>88500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126215</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131606</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174526</t>
+          <t>172108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229320</t>
+          <t>230897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285717</t>
+          <t>287344</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376360</t>
+          <t>376954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>412577</t>
+          <t>414075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>348558</t>
+          <t>350976</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391478</t>
+          <t>390756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739942</t>
+          <t>738315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>796339</t>
+          <t>794762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139000</t>
+          <t>138095</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173422</t>
+          <t>172922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187338</t>
+          <t>187450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>222503</t>
+          <t>222729</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>336164</t>
+          <t>335295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>385729</t>
+          <t>387111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,11%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145143</t>
+          <t>145643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179565</t>
+          <t>180470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113806</t>
+          <t>113580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148971</t>
+          <t>148859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269145</t>
+          <t>267763</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318710</t>
+          <t>319579</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143414</t>
+          <t>144666</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>182822</t>
+          <t>183217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189842</t>
+          <t>188279</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231103</t>
+          <t>228238</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344531</t>
+          <t>345179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>402183</t>
+          <t>401472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187142</t>
+          <t>186747</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226550</t>
+          <t>225298</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156180</t>
+          <t>159045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>197441</t>
+          <t>199004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>355064</t>
+          <t>355775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>412716</t>
+          <t>412068</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,42%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>173351</t>
+          <t>172774</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191828</t>
+          <t>191035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181304</t>
+          <t>182048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200115</t>
+          <t>200576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>359584</t>
+          <t>361382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386022</t>
+          <t>387489</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,15%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19393</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18472</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>36539</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>42319</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70224</t>
+          <t>68426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76410</t>
+          <t>75712</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>107051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>108670</t>
+          <t>107582</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141912</t>
+          <t>142506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194637</t>
+          <t>193527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>239882</t>
+          <t>239654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,69%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155618</t>
+          <t>156072</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186713</t>
+          <t>187411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>131203</t>
+          <t>130609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164445</t>
+          <t>165533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>296356</t>
+          <t>296584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341601</t>
+          <t>342711</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>322642</t>
+          <t>320841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>376137</t>
+          <t>372865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>369187</t>
+          <t>369769</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>422823</t>
+          <t>423392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>707831</t>
+          <t>710494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>782686</t>
+          <t>783953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>280421</t>
+          <t>283693</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>333916</t>
+          <t>335717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>268471</t>
+          <t>267902</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>322107</t>
+          <t>321525</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>565166</t>
+          <t>563899</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640021</t>
+          <t>637358</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>390290</t>
+          <t>393463</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>447412</t>
+          <t>448836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>439059</t>
+          <t>442779</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>499797</t>
+          <t>500499</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>846689</t>
+          <t>848854</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>931619</t>
+          <t>928399</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>57,85%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331171</t>
+          <t>329747</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>388293</t>
+          <t>385120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>326370</t>
+          <t>325668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387108</t>
+          <t>383388</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>676351</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>758061</t>
+          <t>755896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1578751</t>
+          <t>1569963</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1701411</t>
+          <t>1684833</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1884984</t>
+          <t>1877885</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2012236</t>
+          <t>2002874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3483912</t>
+          <t>3488953</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3659063</t>
+          <t>3660935</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,76%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1692939</t>
+          <t>1709517</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1815599</t>
+          <t>1824387</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1532306</t>
+          <t>1541668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1659558</t>
+          <t>1666657</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3279829</t>
+          <t>3277957</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3454980</t>
+          <t>3449939</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>104871</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85062</t>
+          <t>89952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124230</t>
+          <t>124423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>102926</t>
+          <t>111362</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>89080</t>
+          <t>97455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>126691</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,22 +10767,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>207797</t>
+          <t>218541</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185162</t>
+          <t>195597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234319</t>
+          <t>241055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>206572</t>
+          <t>211666</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>187213</t>
+          <t>194422</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>226381</t>
+          <t>228893</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>186709</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171734</t>
+          <t>189370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>200555</t>
+          <t>218606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,27 +10880,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>393280</t>
+          <t>416365</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366758</t>
+          <t>393851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>415915</t>
+          <t>439309</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>142847</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117298</t>
+          <t>122490</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171214</t>
+          <t>175504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>194193</t>
+          <t>204602</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174341</t>
+          <t>186410</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>215320</t>
+          <t>224956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>337040</t>
+          <t>351666</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305548</t>
+          <t>317446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372395</t>
+          <t>385670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374672</t>
+          <t>382593</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346305</t>
+          <t>354154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>400221</t>
+          <t>407168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>319384</t>
+          <t>340430</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>298257</t>
+          <t>320076</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339236</t>
+          <t>358622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>694056</t>
+          <t>723023</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658701</t>
+          <t>689019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725548</t>
+          <t>757243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,46%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517519</t>
+          <t>529658</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513577</t>
+          <t>545032</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031096</t>
+          <t>1074689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83520</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>73418</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99957</t>
+          <t>102870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>129422</t>
+          <t>133088</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>117499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>144472</t>
+          <t>148121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>212942</t>
+          <t>220609</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192313</t>
+          <t>201604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>234516</t>
+          <t>243278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,56%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>230557</t>
+          <t>226551</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214120</t>
+          <t>211201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243465</t>
+          <t>240653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>214683</t>
+          <t>218330</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199633</t>
+          <t>203297</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>230322</t>
+          <t>233919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>445240</t>
+          <t>444881</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>423666</t>
+          <t>422212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>465869</t>
+          <t>463886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>69,71%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>314077</t>
+          <t>314071</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>344105</t>
+          <t>351418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>658182</t>
+          <t>665490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>98340</t>
+          <t>115925</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120029</t>
+          <t>138943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>224166</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>164430</t>
+          <t>151548</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>314072</t>
+          <t>192779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>322506</t>
+          <t>288025</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264951</t>
+          <t>259157</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>457321</t>
+          <t>317928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>207844</t>
+          <t>250216</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>186155</t>
+          <t>227198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>225451</t>
+          <t>271626</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>246313</t>
+          <t>244316</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156407</t>
+          <t>223637</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306049</t>
+          <t>264868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>454157</t>
+          <t>494532</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>319342</t>
+          <t>464629</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>511712</t>
+          <t>523400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>366141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>470479</t>
+          <t>416416</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>776663</t>
+          <t>782557</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>136093</t>
+          <t>153757</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125531</t>
+          <t>140731</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145966</t>
+          <t>164552</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>187013</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163381</t>
+          <t>177052</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>194772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>308909</t>
+          <t>340770</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>294601</t>
+          <t>324453</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>321481</t>
+          <t>355251</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42146</t>
+          <t>51415</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32273</t>
+          <t>40620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52708</t>
+          <t>64441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27150</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43266</t>
+          <t>48085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>75977</t>
+          <t>89539</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63405</t>
+          <t>75058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>105856</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178239</t>
+          <t>205172</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>206647</t>
+          <t>225137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>384886</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>92584</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78591</t>
+          <t>77735</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>106841</t>
+          <t>105300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>96734</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84162</t>
+          <t>86707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109593</t>
+          <t>112224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>189004</t>
+          <t>192001</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>172123</t>
+          <t>173559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>209295</t>
+          <t>210268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>176894</t>
+          <t>177646</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162323</t>
+          <t>164930</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190573</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>164333</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>151526</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172894</t>
+          <t>177043</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>337216</t>
+          <t>341979</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>316925</t>
+          <t>323712</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>354097</t>
+          <t>360421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269164</t>
+          <t>270230</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526220</t>
+          <t>533980</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>324896</t>
+          <t>367088</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293769</t>
+          <t>338428</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>355192</t>
+          <t>399236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>611516</t>
+          <t>485999</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>525784</t>
+          <t>458211</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>734326</t>
+          <t>511293</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>936412</t>
+          <t>853087</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>837413</t>
+          <t>809491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1156375</t>
+          <t>890398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>295005</t>
+          <t>347532</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>264709</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>326132</t>
+          <t>376192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>235348</t>
+          <t>283363</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>258069</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>321080</t>
+          <t>311151</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>530353</t>
+          <t>630895</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>310390</t>
+          <t>593584</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629352</t>
+          <t>674491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>619901</t>
+          <t>714620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846864</t>
+          <t>769362</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466765</t>
+          <t>1483982</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>399864</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>153185</t>
+          <t>368556</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>480900</t>
+          <t>433898</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>428656</t>
+          <t>492607</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>407438</t>
+          <t>464414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>452295</t>
+          <t>518587</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>776364</t>
+          <t>892471</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>447793</t>
+          <t>850357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>919980</t>
+          <t>933478</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>57,45%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>579476</t>
+          <t>396501</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>446284</t>
+          <t>362467</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>773999</t>
+          <t>427809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>286585</t>
+          <t>335844</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>262946</t>
+          <t>309864</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>307803</t>
+          <t>364037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>866061</t>
+          <t>732345</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>722445</t>
+          <t>691338</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1194632</t>
+          <t>774459</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927184</t>
+          <t>796365</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715241</t>
+          <t>828451</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1642425</t>
+          <t>1624816</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1052445</t>
+          <t>1407074</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1456307</t>
+          <t>1533452</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1827309</t>
+          <t>1836258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2268094</t>
+          <t>1940212</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,17 +13511,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2972143</t>
+          <t>3275867</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3633796</t>
+          <t>3442213</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>47,61%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2113167</t>
+          <t>2044121</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1987404</t>
+          <t>1981651</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2391266</t>
+          <t>2108029</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1683174</t>
+          <t>1829439</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1375509</t>
+          <t>1775415</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1816294</t>
+          <t>1879369</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,17 +13624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3796341</t>
+          <t>3873560</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3453518</t>
+          <t>3788517</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4115171</t>
+          <t>3954863</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3443711</t>
+          <t>3515103</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3643603</t>
+          <t>3715627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7087314</t>
+          <t>7230730</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
